--- a/ted_tenders.xlsx
+++ b/ted_tenders.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Live Opportunities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Market Intelligence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,4 +508,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>deadline</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>buyer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>notice_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>t1_hits</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Denmark – Research and development services and related consultancy services – Media management services for EIT Food</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aarhus Universitet</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>can-standard</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>eit food</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/307243-2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ted_tenders.xlsx
+++ b/ted_tenders.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Live Opportunities" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Market Intelligence" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Market Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,108 +413,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>bucket</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>deadline</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>buyer</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>notice_type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>t1_hits</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Live opportunity</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Germany – Feasibility study, advisory service, analysis – Bodenstationsnetzwerk-Service für die Kleinsatellitenmission ROMEO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Universität Stuttgart</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>cn-standard</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://ted.europa.eu/en/notice/-/detail/301891-2026</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/ted_tenders.xlsx
+++ b/ted_tenders.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Market Intelligence" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live Opportunities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Intelligence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +426,257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>deadline</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>buyer</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>notice_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>t1_hits</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Live opportunity</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Norway – Research and development consultancy services – Commercialisation services</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NORCE Research AS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>cn-standard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>commercialisation services</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/311955-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Possible opportunity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Germany – Evaluation consultancy services – 6#0040/E21 Evaluierung des Verfahrens der fahrplanbasierten Infrastrukturentwicklung auf Grundlage des Zielfahrplans Deutschlandtakt</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bundesministerium für Verkehr, H14/Servicestelle-Vergabe</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>cn-standard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/318148-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Possible opportunity</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Germany – Foreign economic-aid-related services – 10014668-Asesoría técnica para el acompañamiento del proceso de acceso y post acceso del Perú a OCDE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) GmbH</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>cn-standard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/326886-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Possible opportunity</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Germany – Foreign economic-aid-related services – 10003421-Early-stage infrastructure project preparation via the AUDA-NEPAD Service Delivery Mechanism</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) GmbH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>cn-standard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/327009-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Possible opportunity</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Germany – Business and management consultancy services – Umsetzung der Handlungsfelder aus der Prozessanalyse zur Optimierung aller Abrechnungsarten inkl. Forderungsmanagement</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Universitätsklinikum Regensburg AöR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>veat</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/332998-2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -421,42 +684,42 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>buyer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>notice_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>t1_hits</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
@@ -464,36 +727,211 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ireland – Market research services – Provision of Consultancy Services for Market Insight, Go-To-Market Strategy, Brand Strategy and Visual Identity Development – Reddot Food Limited</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Reddot Food</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>can-standard</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>go-to-market strategy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/305782-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>4</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Denmark – Research and development services and related consultancy services – Media management services for EIT Food</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Aarhus Universitet</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Spain – Financial and insurance services – Rfp CFS Audit Services</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>can-standard</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>eit food</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://ted.europa.eu/en/notice/-/detail/307243-2026</t>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>eit urban mobility</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/324404-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Spain – IT services: consulting, software development, Internet and support – Rfp Digital &amp; Private Platform for EIT Urban Mobility Community - “Mobility Innovators”, 26-28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>can-standard</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>eit urban mobility</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/330268-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Spain – Business services: law, marketing, consulting, recruitment, printing and security – Rfp Implementation of Digital Marketing and Dissemination Activities for the EIT Campus ´26-28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>can-standard</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>eit urban mobility</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/330885-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Spain – IT services: consulting, software development, Internet and support – Rfp EIT Campus Platform Tool Development ´26-28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>can-standard</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>eit urban mobility</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/331604-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Spain – Business services: law, marketing, consulting, recruitment, printing and security – Rfp Implementation of Marketing, Communication and Content Activities for the EIT STEM Tech Talent Initiative ´26-28</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>can-standard</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>eit urban mobility</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/en/notice/-/detail/334307-2026</t>
         </is>
       </c>
     </row>
